--- a/output/stock_quant_scores/TSMC34.SA_info.xlsx
+++ b/output/stock_quant_scores/TSMC34.SA_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ET2"/>
+  <dimension ref="A1:ES2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,200 +976,195 @@
       </c>
       <c r="DG1" s="1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
       <c r="EQ1" s="1" t="inlineStr">
         <is>
-          <t>marketState</t>
+          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="ER1" s="1" t="inlineStr">
         <is>
-          <t>regularMarketChangePercent</t>
+          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1259,7 +1254,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. C. C.  Wei Ph.D.', 'title': 'Chairman &amp; CEO', 'fiscalYear': 2024, 'totalPay': 116210503, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jen-Chau  Huang', 'title': 'Senior VP of Finance &amp; CFO', 'fiscalYear': 2024, 'totalPay': 26485266, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Y. P.  Chyn', 'title': 'Executive VP of Operations &amp; Co-COO', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Y. J. Mii', 'title': 'Executive VP &amp; Co-COO', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Horng-Dar  Lin', 'title': 'Vice President of Corporate Information Technology &amp; Chief Information Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jeff  Su', 'title': 'Director of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sylvia  Fang', 'title': 'Senior VP of Legal, General Counsel &amp; Corporate Governance Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Elizabeth  Sun', 'title': 'Senior Director of Corporate Communication Division', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Nan Lok  Chen GBS, JP', 'age': 68, 'title': 'Vice President of the Human Resources', 'yearBorn': 1956, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Li Mei  He Ho', 'title': 'Senior Vice President of Corporate Strategy Development', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Dr. C. C.  Wei Ph.D.', 'title': 'Chairman &amp; CEO', 'fiscalYear': 2024, 'totalPay': 115311352, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jen-Chau  Huang', 'title': 'Senior VP of Finance &amp; CFO', 'fiscalYear': 2024, 'totalPay': 26280343, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Y. P.  Chyn', 'title': 'Executive VP of Operations &amp; Co-COO', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Y. J. Mii', 'title': 'Executive VP &amp; Co-COO', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Horng-Dar  Lin', 'title': 'Vice President of Corporate Information Technology &amp; Chief Information Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jeff  Su', 'title': 'Director of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sylvia  Fang', 'title': 'Senior VP of Legal, General Counsel &amp; Corporate Governance Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Elizabeth  Sun', 'title': 'Senior Director of Corporate Communication Division', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Nan Lok  Chen GBS, JP', 'age': 68, 'title': 'Vice President of the Human Resources', 'yearBorn': 1956, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Li Mei  He Ho', 'title': 'Senior Vice President of Corporate Strategy Development', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -1282,34 +1277,34 @@
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>186.69</v>
+        <v>185.74</v>
       </c>
       <c r="Y2" t="n">
-        <v>186.69</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>183.81</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>186.69</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>186.69</v>
+        <v>185.74</v>
       </c>
       <c r="AC2" t="n">
-        <v>186.69</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>183.81</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>186.69</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="AH2" t="n">
         <v>1765324800</v>
@@ -1324,58 +1319,58 @@
         <v>1.199</v>
       </c>
       <c r="AL2" t="n">
-        <v>30.338762</v>
+        <v>29.695581</v>
       </c>
       <c r="AM2" t="n">
-        <v>23064</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>23064</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>39399</v>
+        <v>39451</v>
       </c>
       <c r="AP2" t="n">
-        <v>56679</v>
+        <v>58315</v>
       </c>
       <c r="AQ2" t="n">
-        <v>56679</v>
+        <v>58315</v>
       </c>
       <c r="AR2" t="n">
-        <v>186.12</v>
+        <v>180.53</v>
       </c>
       <c r="AS2" t="n">
-        <v>186.28</v>
+        <v>182.69</v>
       </c>
       <c r="AT2" t="n">
-        <v>7729164320768</v>
+        <v>7528342093824</v>
       </c>
       <c r="AU2" t="n">
-        <v>98.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>189.81</v>
+        <v>189.94</v>
       </c>
       <c r="AW2" t="n">
-        <v>189.81</v>
+        <v>189.94</v>
       </c>
       <c r="AX2" t="n">
         <v>25.81875</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.2724824</v>
+        <v>2.2134378</v>
       </c>
       <c r="AZ2" t="n">
-        <v>166.0704</v>
+        <v>167.0724</v>
       </c>
       <c r="BA2" t="n">
-        <v>146.29926</v>
+        <v>146.76724</v>
       </c>
       <c r="BB2" t="n">
         <v>19</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.101772994</v>
+        <v>0.10229353</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1386,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>3257229377536</v>
+        <v>3121083318272</v>
       </c>
       <c r="BG2" t="n">
         <v>0.42481998</v>
@@ -1410,7 +1405,7 @@
         <v>176.653</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.0544966</v>
+        <v>1.0270983</v>
       </c>
       <c r="BO2" t="n">
         <v>1735603200</v>
@@ -1428,7 +1423,7 @@
         <v>1444887003136</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.14</v>
+        <v>6.11</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -1439,16 +1434,16 @@
         <v>1603929600</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.958</v>
+        <v>0.918</v>
       </c>
       <c r="BX2" t="n">
-        <v>1.386</v>
+        <v>1.328</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.49387848</v>
+        <v>0.53710604</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CA2" t="n">
         <v>0.445575</v>
@@ -1462,7 +1457,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>186.28</v>
+        <v>181.44</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -1566,147 +1561,144 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DH2" t="n">
-        <v>1758739116</v>
-      </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DI2" t="n">
+        <v>1758929595</v>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1572008400000</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-4.300003</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>0.0 - 0.0</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>39451</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>181.44</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>0.0 - 189.94</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.044750974</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>53.7106</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1752663540</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1753272000</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1744869600</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1744869600</v>
+      </c>
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>TAIWANSMFAC DRN ED</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>14.3675995</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0.08599625</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>34.67276</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.23624317</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>SAO</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>finmb_380075</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>America/Sao_Paulo</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>BRT</t>
         </is>
       </c>
-      <c r="DM2" t="n">
+      <c r="EN2" t="n">
         <v>-10800000</v>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="EO2" t="inlineStr">
         <is>
           <t>br_market</t>
         </is>
       </c>
-      <c r="DO2" t="b">
+      <c r="EP2" t="b">
         <v>0</v>
       </c>
-      <c r="DP2" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>20.209595</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.12169293</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>39.980743</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.27328056</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1572008400000</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.41000366</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>183.81 - 186.69</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>39399</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>87.45999999999999</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.8850435</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>98.82 - 189.81</t>
-        </is>
-      </c>
-      <c r="EG2" t="n">
-        <v>-3.5299988</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.01859754</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>49.387848</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1752663540</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1753272000</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>1744869600</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1744869600</v>
-      </c>
-      <c r="EN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>TAIWANSMFAC DRN ED</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
+      <c r="EQ2" t="n">
+        <v>-2.3150656</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.21962912</v>
+        <v>181.44</v>
       </c>
       <c r="ES2" t="n">
-        <v>186.28</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>1.4614</v>
+        <v>1.4292</v>
       </c>
     </row>
   </sheetData>
